--- a/UP_Quarry_Site_Tracker.xlsx
+++ b/UP_Quarry_Site_Tracker.xlsx
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Jacobsville Sandstone</t>
+          <t>Dolostone</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -1306,12 +1306,13 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>T46N R17W S28</t>
+          <t>T46N R18W S24
+SE¼</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>46.5617, -86.6042</t>
+          <t>46.3710, -86.5160</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1321,7 +1322,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Lindberg &amp; Sons operation; active sandstone quarry. Thin veneer potential.</t>
+          <t>A. Lindberg &amp; Sons aggregate pit off M28 on Percy Rd. Blue-grey to tan dolostone, beds 3-12" thick. One of 2 Alger Co. dolostones rated suitable for dimension stone.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -1336,7 +1337,7 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>599 Washington St, Ishpeming, MI 49849</t>
+          <t>5741 Percy Road (Co Rd 653), Shingleton, MI 49884</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
@@ -1346,7 +1347,7 @@
       </c>
       <c r="L15" s="8" t="inlineStr">
         <is>
-          <t>Call to confirm lease/sale interest</t>
+          <t>Call to confirm lease/sale interest. Active dolostone pit off M28 on Percy Road</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1607,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Dolostone (Randville)</t>
+          <t>Tremolitic Marble</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1616,12 +1617,13 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>T40N R30W S22</t>
+          <t>T42N R30W S34
+NE¼ SE¼</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>45.8667, -88.0833</t>
+          <t>45.9970, -88.0460</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1631,7 +1633,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Randville Dolostone outcrop; hard, dense, good for veneer if not too fractured.</t>
+          <t>Crystalline marble — white, pink, pale green, faint blue. Cut in Randville dolomite ridge, 1 mi E of M95/railroad at Randville. Beds strike N20E dip 77N.</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -1656,7 +1658,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Research parcel ownership</t>
+          <t>Research parcel near Randville, MI. Promising ornamental marble.</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1670,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Dolostone (Randville)</t>
+          <t>Sandstone</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1678,12 +1680,13 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>T40N R30W S14</t>
+          <t>T42N R29W S30
+SW¼</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>45.8833, -88.0833</t>
+          <t>46.0080, -87.9940</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1693,17 +1696,17 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Same formation as Site 20; adjacent parcel may be same owner.</t>
+          <t>Groveland Mine area. Buff to tan/orange/brick-red carbonate-cemented sandstone. Beds 8-12" flat-lying. Study rates No Potential — colors not impressive.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>VERIFY</t>
+          <t>NOT VIABLE</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Private / Unknown</t>
+          <t>Groveland Mine / Private</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1718,7 +1721,7 @@
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
-          <t>Cross-reference with Site 20 owner</t>
+          <t>No dimension stone potential per study.</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1743,13 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>T40N R29W S8</t>
+          <t>T42N R29W S30
+SW¼ SE¼</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>45.9000, -87.9583</t>
+          <t>46.0080,-87.9870</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1755,7 +1759,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Dark amphibolite; potential for black accent stone. Verify quarryability.</t>
+          <t>Near Groveland Mine road. Very dark green, glistening amphibole. Quarried intermittently for terrazzo/aggregate. Rusty brown weathered. Jointing strikes N10E.</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1780,7 +1784,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>Ownership research needed</t>
+          <t>Research parcel. Confirm quarryability for veneer.</t>
         </is>
       </c>
     </row>
@@ -1792,22 +1796,24 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Black Jaspilite / BIF</t>
+          <t>Granite + Marble
+(Felch Quarry)</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Dickinson</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>T47N R26W S16</t>
+          <t>T42N R28W S26
+S½</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>46.6167, -87.8333</t>
+          <t>46.0220,-87.7580</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1817,7 +1823,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>Banded Iron Formation; striking black/red banding. Decorative veneer potential. Hard material.</t>
+          <t>Site 24: pink granite aplite dikes 2.5-12 ft wide in Felch Quarry workings. Site 25: coarse white marble w/pale green tremolite. Part-time crushing operation active 1999.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -1827,22 +1833,22 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>State / Private</t>
+          <t>Felch Quarry Co. / Private</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>EGLE or Marquette Co. Register of Deeds</t>
+          <t>Dickinson Co. Register of Deeds, Iron Mountain</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>(906) 225-8415</t>
+          <t>(906) 774-0955</t>
         </is>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
-          <t>Confirm state vs. private; check mining permits</t>
+          <t>Contact Felch Quarry re: stone availability. Confirm current operation.</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1860,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Granite Gneiss</t>
+          <t>Sandstone</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1864,7 +1870,8 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>T42N R30W S4</t>
+          <t>T42N R30W S4
+SW¼ NW¼</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1879,7 +1886,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>Granite gneiss outcrop in forested area. Good dimensional stone potential.</t>
+          <t>Outcrop adjacent to M95. Tan, buff, reddish-brown sandstone, distinctly bedded. Similar mineralogy to Site 21 (Groveland).</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -1904,7 +1911,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Confirm parcel; negotiate surface rights for stone</t>
+          <t>Negotiate surface rights for stone extraction.</t>
         </is>
       </c>
     </row>
@@ -1926,12 +1933,13 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>T39N R29W S6</t>
+          <t>T39N R29W S9
+NW¼ NW¼</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>45.8250, -87.9583</t>
+          <t>45.8000, -87.9350</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1941,7 +1949,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>Mayville Dolostone near Norway, MI. Study may have PLSS typo (listed R24W, likely R29W).</t>
+          <t>Road metal quarry E of Strawberry Lake, N edge of Norway. Pink, grey, tannish-pink, blue-grey dolostone. Beds 3-12" thick. Note: study historical notes say R24W (likely typo; site location says R29W).</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -1966,7 +1974,7 @@
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
-          <t>Confirm PLSS coords; research parcel owner</t>
+          <t>Research parcel at S9 T39N R29W. Confirm current ownership.</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1986,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Felsite Conglomerate</t>
+          <t>Dolostone</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1988,12 +1996,13 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>T40N R22W S30</t>
+          <t>T40N R19W S3
+NW¼ SE¼</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>45.8500, -87.1667</t>
+          <t>45.8960, -86.6620</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2003,7 +2012,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Thornton Construction site; colorful felsite conglomerate, ornamental potential.</t>
+          <t>Thornton Construction pit immediately adjacent to US-2. Blue-grey to buff dolostone. One of only 2 Delta Co. sites rated suitable for dimension stone. Beds confirmed for veneer potential.</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -2013,22 +2022,22 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Thornton Construction</t>
+          <t>Thornton Construction Co.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Escanaba area, Delta Co., MI</t>
+          <t>1028 Ethel Ave, Hancock, MI 49930</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>(906) 786-XXXX</t>
+          <t>(906) 482-2122</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Contact re: stone availability / lease</t>
+          <t>Contact Thornton in Hancock re: stone availability / lease.</t>
         </is>
       </c>
     </row>

--- a/UP_Quarry_Site_Tracker.xlsx
+++ b/UP_Quarry_Site_Tracker.xlsx
@@ -1312,7 +1312,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>46.3710, -86.5160</t>
+          <t>46.3673, -86.4901</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
